--- a/inbox-excel-vocabs/voc4cat.xlsx
+++ b/inbox-excel-vocabs/voc4cat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\working group\Franzi\Research Data Managment\Voc4Cat\FF_20250328_Voc4Cat contributions\Revision ab august\selected concepts 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B5AE0B-FCA6-4C98-B88F-D61C9E0617BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{347A717F-27FD-45B2-B2A2-28317099230E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="652" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="652" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Introduction" sheetId="1" r:id="rId1"/>
@@ -6650,68 +6650,6 @@
     <t>voc4cat:0007840 (solvation)</t>
   </si>
   <si>
-    <t>voc4cat:0000007 (Fermi level),
-voc4cat:0000011 (valence band),
-voc4cat:0000012 (conduction band),
-voc4cat:0000055 (calcination gaseous environment),
-voc4cat:0000062 (chemical substance for synthesis),
-voc4cat:0000084 (electronic state),
-voc4cat:0000101 (reactant),
-voc4cat:0000105 (sacrificial reagant),
-voc4cat:0000128 (photoreactor design),
-voc4cat:0000177 (infrared),
-voc4cat:0000178 (visible),
-voc4cat:0000179 (ultraviolet),
-voc4cat:0000196 (catalysis research field),
-voc4cat:0000199 (reaction mechanism),
-voc4cat:0000200 (green chemistry),
-voc4cat:0000201 (cross-coupling reaction),
-voc4cat:0000203 (photochemistry),
-voc4cat:0000215 (density functional theory),
-voc4cat:0000218 (electrochemistry),
-voc4cat:0000219 (heterocycle),
-voc4cat:0000225 (structure-activity relationship),
-voc4cat:0000229 (radical),
-voc4cat:0000231 (renewable resource),
-voc4cat:0000235 (synergistic effect),
-voc4cat:0000238 (surface chemistry),
-voc4cat:0000240 (stereoisomer),
-voc4cat:0000255 (magnetic property),
-voc4cat:0000257 (solvent effect),
-voc4cat:0000263 (stereoselectivity),
-voc4cat:0000264 (computational chemistry),
-voc4cat:0000267 (bifunctional catalyst),
-voc4cat:0000274 (diastereoselectivity),
-voc4cat:0000275 (water chemistry),
-voc4cat:0000277 (C-H functionalization),
-voc4cat:0000279 (oxygen vacancy),
-voc4cat:0000284 (nitrogen heterocycle),
-voc4cat:0000287 (ligand),
-voc4cat:0000292 (Fischer-Tropsch technology),
-voc4cat:0000298 (kinetics),
-voc4cat:0000301 (Lewis acid),
-voc4cat:0000309 (transition metal),
-voc4cat:0005011 (PID resource categories),
-voc4cat:0005018 (resource relation),
-voc4cat:0005051 (pid4cat status),
-voc4cat:0005058 (statistical sample),
-voc4cat:0007005 (reagent),
-voc4cat:0007006 (active site),
-voc4cat;0007794 (precursor)
-voc4cat:0007040 (chemical reaction mechanism),
-voc4cat:0007041 (elementary reaction),
-voc4cat:0007101 (reactor model type),
-voc4cat:0007246 (solvent),
-voc4cat:0007247 (solute),
-voc4cat:0007811 (liquid sample),
-voc4cat:0007812 (gaseous sample)
-voc4cat:0007828 (external standard),
-voc4cat:0007829 (internal standard),
-voc4cat:0007809 (atmosphere),
-voc4cat:0007838 (product mixture),
-voc4cat:0007793 (additive)</t>
-  </si>
-  <si>
     <t>voc4cat:0007803</t>
   </si>
   <si>
@@ -6845,6 +6783,68 @@
 voc4cat:0007844 (molar equivalent),
 voc4cat:0007817 (turnover frequency),
 voc4cat:0007803 (turnover number)</t>
+  </si>
+  <si>
+    <t>voc4cat:0000007 (Fermi level),
+voc4cat:0000011 (valence band),
+voc4cat:0000012 (conduction band),
+voc4cat:0000055 (calcination gaseous environment),
+voc4cat:0000062 (chemical substance for synthesis),
+voc4cat:0000084 (electronic state),
+voc4cat:0000101 (reactant),
+voc4cat:0000105 (sacrificial reagant),
+voc4cat:0000128 (photoreactor design),
+voc4cat:0000177 (infrared),
+voc4cat:0000178 (visible),
+voc4cat:0000179 (ultraviolet),
+voc4cat:0000196 (catalysis research field),
+voc4cat:0000199 (reaction mechanism),
+voc4cat:0000200 (green chemistry),
+voc4cat:0000201 (cross-coupling reaction),
+voc4cat:0000203 (photochemistry),
+voc4cat:0000215 (density functional theory),
+voc4cat:0000218 (electrochemistry),
+voc4cat:0000219 (heterocycle),
+voc4cat:0000225 (structure-activity relationship),
+voc4cat:0000229 (radical),
+voc4cat:0000231 (renewable resource),
+voc4cat:0000235 (synergistic effect),
+voc4cat:0000238 (surface chemistry),
+voc4cat:0000240 (stereoisomer),
+voc4cat:0000255 (magnetic property),
+voc4cat:0000257 (solvent effect),
+voc4cat:0000263 (stereoselectivity),
+voc4cat:0000264 (computational chemistry),
+voc4cat:0000267 (bifunctional catalyst),
+voc4cat:0000274 (diastereoselectivity),
+voc4cat:0000275 (water chemistry),
+voc4cat:0000277 (C-H functionalization),
+voc4cat:0000279 (oxygen vacancy),
+voc4cat:0000284 (nitrogen heterocycle),
+voc4cat:0000287 (ligand),
+voc4cat:0000292 (Fischer-Tropsch technology),
+voc4cat:0000298 (kinetics),
+voc4cat:0000301 (Lewis acid),
+voc4cat:0000309 (transition metal),
+voc4cat:0005011 (PID resource categories),
+voc4cat:0005018 (resource relation),
+voc4cat:0005051 (pid4cat status),
+voc4cat:0005058 (statistical sample),
+voc4cat:0007005 (reagent),
+voc4cat:0007006 (active site),
+voc4cat:0007794 (precursor)
+voc4cat:0007040 (chemical reaction mechanism),
+voc4cat:0007041 (elementary reaction),
+voc4cat:0007101 (reactor model type),
+voc4cat:0007246 (solvent),
+voc4cat:0007247 (solute),
+voc4cat:0007811 (liquid sample),
+voc4cat:0007812 (gaseous sample)
+voc4cat:0007828 (external standard),
+voc4cat:0007829 (internal standard),
+voc4cat:0007809 (atmosphere),
+voc4cat:0007838 (product mixture),
+voc4cat:0007793 (additive)</t>
   </si>
 </sst>
 </file>
@@ -7095,7 +7095,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -7188,13 +7188,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -7213,23 +7206,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="7" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -7765,65 +7750,65 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="37"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="12"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
       <c r="L16" s="12"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
       <c r="L17" s="12"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
@@ -7926,61 +7911,61 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
@@ -8044,391 +8029,391 @@
       <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="36" t="s">
+      <c r="B12" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="37"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
     </row>
     <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="37"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37"/>
-      <c r="J14" s="37"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="37"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="44"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="37"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="37"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="37"/>
-      <c r="C26" s="37"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37"/>
-      <c r="H26" s="37"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="37"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="44"/>
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="37"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="37"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="44"/>
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="37"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="37"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="37"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="44"/>
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="37"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
-      <c r="H30" s="37"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="37"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="37"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="37"/>
-      <c r="J31" s="37"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="44"/>
+      <c r="J31" s="44"/>
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="37"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="37"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="37"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="37"/>
-      <c r="I33" s="37"/>
-      <c r="J33" s="37"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="44"/>
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="37"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="44"/>
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="37"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="37"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="44"/>
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="37"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="37"/>
-      <c r="H36" s="37"/>
-      <c r="I36" s="37"/>
-      <c r="J36" s="37"/>
+      <c r="B36" s="44"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="44"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="44"/>
+      <c r="J36" s="44"/>
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="37"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="37"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="44"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="44"/>
+      <c r="J37" s="44"/>
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="37"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="37"/>
-      <c r="H38" s="37"/>
-      <c r="I38" s="37"/>
-      <c r="J38" s="37"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="44"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="44"/>
+      <c r="I38" s="44"/>
+      <c r="J38" s="44"/>
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="37"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="37"/>
-      <c r="I39" s="37"/>
-      <c r="J39" s="37"/>
+      <c r="B39" s="44"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="44"/>
+      <c r="E39" s="44"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="44"/>
+      <c r="I39" s="44"/>
+      <c r="J39" s="44"/>
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="37"/>
-      <c r="J40" s="37"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="44"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="44"/>
+      <c r="I40" s="44"/>
+      <c r="J40" s="44"/>
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="37"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
-      <c r="J41" s="37"/>
+      <c r="B41" s="44"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="44"/>
+      <c r="E41" s="44"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="44"/>
+      <c r="H41" s="44"/>
+      <c r="I41" s="44"/>
+      <c r="J41" s="44"/>
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="37"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="37"/>
-      <c r="J42" s="37"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="44"/>
+      <c r="E42" s="44"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="44"/>
+      <c r="H42" s="44"/>
+      <c r="I42" s="44"/>
+      <c r="J42" s="44"/>
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="37"/>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="37"/>
-      <c r="J43" s="37"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="37"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="37"/>
-      <c r="I44" s="37"/>
-      <c r="J44" s="37"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="44"/>
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="37"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="37"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="37"/>
-      <c r="I45" s="37"/>
-      <c r="J45" s="37"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="44"/>
+      <c r="J45" s="44"/>
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="37"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="37"/>
-      <c r="H46" s="37"/>
-      <c r="I46" s="37"/>
-      <c r="J46" s="37"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="44"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="44"/>
+      <c r="J46" s="44"/>
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C47" s="1"/>
@@ -8441,1074 +8426,1074 @@
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="36" t="s">
+      <c r="B48" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="37"/>
-      <c r="I48" s="37"/>
-      <c r="J48" s="37"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="44"/>
+      <c r="F48" s="44"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="44"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="44"/>
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="37"/>
-      <c r="C49" s="37"/>
-      <c r="D49" s="37"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="37"/>
-      <c r="H49" s="37"/>
-      <c r="I49" s="37"/>
-      <c r="J49" s="37"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="44"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="44"/>
+      <c r="F49" s="44"/>
+      <c r="G49" s="44"/>
+      <c r="H49" s="44"/>
+      <c r="I49" s="44"/>
+      <c r="J49" s="44"/>
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="37"/>
-      <c r="C50" s="37"/>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="37"/>
-      <c r="I50" s="37"/>
-      <c r="J50" s="37"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="44"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
+      <c r="I50" s="44"/>
+      <c r="J50" s="44"/>
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="37"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="37"/>
-      <c r="H51" s="37"/>
-      <c r="I51" s="37"/>
-      <c r="J51" s="37"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="44"/>
+      <c r="D51" s="44"/>
+      <c r="E51" s="44"/>
+      <c r="F51" s="44"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="44"/>
+      <c r="I51" s="44"/>
+      <c r="J51" s="44"/>
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="37"/>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="37"/>
-      <c r="H52" s="37"/>
-      <c r="I52" s="37"/>
-      <c r="J52" s="37"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="44"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="44"/>
+      <c r="G52" s="44"/>
+      <c r="H52" s="44"/>
+      <c r="I52" s="44"/>
+      <c r="J52" s="44"/>
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="37"/>
-      <c r="C53" s="37"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="37"/>
-      <c r="G53" s="37"/>
-      <c r="H53" s="37"/>
-      <c r="I53" s="37"/>
-      <c r="J53" s="37"/>
+      <c r="B53" s="44"/>
+      <c r="C53" s="44"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="44"/>
+      <c r="J53" s="44"/>
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="37"/>
-      <c r="C54" s="37"/>
-      <c r="D54" s="37"/>
-      <c r="E54" s="37"/>
-      <c r="F54" s="37"/>
-      <c r="G54" s="37"/>
-      <c r="H54" s="37"/>
-      <c r="I54" s="37"/>
-      <c r="J54" s="37"/>
+      <c r="B54" s="44"/>
+      <c r="C54" s="44"/>
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="44"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="44"/>
+      <c r="J54" s="44"/>
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="37"/>
-      <c r="C55" s="37"/>
-      <c r="D55" s="37"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="37"/>
-      <c r="G55" s="37"/>
-      <c r="H55" s="37"/>
-      <c r="I55" s="37"/>
-      <c r="J55" s="37"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="44"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="44"/>
+      <c r="I55" s="44"/>
+      <c r="J55" s="44"/>
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="37"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
-      <c r="H56" s="37"/>
-      <c r="I56" s="37"/>
-      <c r="J56" s="37"/>
+      <c r="B56" s="44"/>
+      <c r="C56" s="44"/>
+      <c r="D56" s="44"/>
+      <c r="E56" s="44"/>
+      <c r="F56" s="44"/>
+      <c r="G56" s="44"/>
+      <c r="H56" s="44"/>
+      <c r="I56" s="44"/>
+      <c r="J56" s="44"/>
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="37"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="37"/>
-      <c r="H57" s="37"/>
-      <c r="I57" s="37"/>
-      <c r="J57" s="37"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="44"/>
+      <c r="D57" s="44"/>
+      <c r="E57" s="44"/>
+      <c r="F57" s="44"/>
+      <c r="G57" s="44"/>
+      <c r="H57" s="44"/>
+      <c r="I57" s="44"/>
+      <c r="J57" s="44"/>
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="37"/>
-      <c r="I58" s="37"/>
-      <c r="J58" s="37"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
+      <c r="F58" s="44"/>
+      <c r="G58" s="44"/>
+      <c r="H58" s="44"/>
+      <c r="I58" s="44"/>
+      <c r="J58" s="44"/>
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="37"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="37"/>
-      <c r="H59" s="37"/>
-      <c r="I59" s="37"/>
-      <c r="J59" s="37"/>
+      <c r="B59" s="44"/>
+      <c r="C59" s="44"/>
+      <c r="D59" s="44"/>
+      <c r="E59" s="44"/>
+      <c r="F59" s="44"/>
+      <c r="G59" s="44"/>
+      <c r="H59" s="44"/>
+      <c r="I59" s="44"/>
+      <c r="J59" s="44"/>
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="37"/>
-      <c r="C60" s="37"/>
-      <c r="D60" s="37"/>
-      <c r="E60" s="37"/>
-      <c r="F60" s="37"/>
-      <c r="G60" s="37"/>
-      <c r="H60" s="37"/>
-      <c r="I60" s="37"/>
-      <c r="J60" s="37"/>
+      <c r="B60" s="44"/>
+      <c r="C60" s="44"/>
+      <c r="D60" s="44"/>
+      <c r="E60" s="44"/>
+      <c r="F60" s="44"/>
+      <c r="G60" s="44"/>
+      <c r="H60" s="44"/>
+      <c r="I60" s="44"/>
+      <c r="J60" s="44"/>
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="37"/>
-      <c r="C61" s="37"/>
-      <c r="D61" s="37"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="37"/>
-      <c r="G61" s="37"/>
-      <c r="H61" s="37"/>
-      <c r="I61" s="37"/>
-      <c r="J61" s="37"/>
+      <c r="B61" s="44"/>
+      <c r="C61" s="44"/>
+      <c r="D61" s="44"/>
+      <c r="E61" s="44"/>
+      <c r="F61" s="44"/>
+      <c r="G61" s="44"/>
+      <c r="H61" s="44"/>
+      <c r="I61" s="44"/>
+      <c r="J61" s="44"/>
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="37"/>
-      <c r="C62" s="37"/>
-      <c r="D62" s="37"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="37"/>
-      <c r="G62" s="37"/>
-      <c r="H62" s="37"/>
-      <c r="I62" s="37"/>
-      <c r="J62" s="37"/>
+      <c r="B62" s="44"/>
+      <c r="C62" s="44"/>
+      <c r="D62" s="44"/>
+      <c r="E62" s="44"/>
+      <c r="F62" s="44"/>
+      <c r="G62" s="44"/>
+      <c r="H62" s="44"/>
+      <c r="I62" s="44"/>
+      <c r="J62" s="44"/>
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="37"/>
-      <c r="C63" s="37"/>
-      <c r="D63" s="37"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
-      <c r="G63" s="37"/>
-      <c r="H63" s="37"/>
-      <c r="I63" s="37"/>
-      <c r="J63" s="37"/>
+      <c r="B63" s="44"/>
+      <c r="C63" s="44"/>
+      <c r="D63" s="44"/>
+      <c r="E63" s="44"/>
+      <c r="F63" s="44"/>
+      <c r="G63" s="44"/>
+      <c r="H63" s="44"/>
+      <c r="I63" s="44"/>
+      <c r="J63" s="44"/>
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="37"/>
-      <c r="C64" s="37"/>
-      <c r="D64" s="37"/>
-      <c r="E64" s="37"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="37"/>
-      <c r="H64" s="37"/>
-      <c r="I64" s="37"/>
-      <c r="J64" s="37"/>
+      <c r="B64" s="44"/>
+      <c r="C64" s="44"/>
+      <c r="D64" s="44"/>
+      <c r="E64" s="44"/>
+      <c r="F64" s="44"/>
+      <c r="G64" s="44"/>
+      <c r="H64" s="44"/>
+      <c r="I64" s="44"/>
+      <c r="J64" s="44"/>
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="37"/>
-      <c r="C65" s="37"/>
-      <c r="D65" s="37"/>
-      <c r="E65" s="37"/>
-      <c r="F65" s="37"/>
-      <c r="G65" s="37"/>
-      <c r="H65" s="37"/>
-      <c r="I65" s="37"/>
-      <c r="J65" s="37"/>
+      <c r="B65" s="44"/>
+      <c r="C65" s="44"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="44"/>
+      <c r="F65" s="44"/>
+      <c r="G65" s="44"/>
+      <c r="H65" s="44"/>
+      <c r="I65" s="44"/>
+      <c r="J65" s="44"/>
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="37"/>
-      <c r="C66" s="37"/>
-      <c r="D66" s="37"/>
-      <c r="E66" s="37"/>
-      <c r="F66" s="37"/>
-      <c r="G66" s="37"/>
-      <c r="H66" s="37"/>
-      <c r="I66" s="37"/>
-      <c r="J66" s="37"/>
+      <c r="B66" s="44"/>
+      <c r="C66" s="44"/>
+      <c r="D66" s="44"/>
+      <c r="E66" s="44"/>
+      <c r="F66" s="44"/>
+      <c r="G66" s="44"/>
+      <c r="H66" s="44"/>
+      <c r="I66" s="44"/>
+      <c r="J66" s="44"/>
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="37"/>
-      <c r="C67" s="37"/>
-      <c r="D67" s="37"/>
-      <c r="E67" s="37"/>
-      <c r="F67" s="37"/>
-      <c r="G67" s="37"/>
-      <c r="H67" s="37"/>
-      <c r="I67" s="37"/>
-      <c r="J67" s="37"/>
+      <c r="B67" s="44"/>
+      <c r="C67" s="44"/>
+      <c r="D67" s="44"/>
+      <c r="E67" s="44"/>
+      <c r="F67" s="44"/>
+      <c r="G67" s="44"/>
+      <c r="H67" s="44"/>
+      <c r="I67" s="44"/>
+      <c r="J67" s="44"/>
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="37"/>
-      <c r="C68" s="37"/>
-      <c r="D68" s="37"/>
-      <c r="E68" s="37"/>
-      <c r="F68" s="37"/>
-      <c r="G68" s="37"/>
-      <c r="H68" s="37"/>
-      <c r="I68" s="37"/>
-      <c r="J68" s="37"/>
+      <c r="B68" s="44"/>
+      <c r="C68" s="44"/>
+      <c r="D68" s="44"/>
+      <c r="E68" s="44"/>
+      <c r="F68" s="44"/>
+      <c r="G68" s="44"/>
+      <c r="H68" s="44"/>
+      <c r="I68" s="44"/>
+      <c r="J68" s="44"/>
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="37"/>
-      <c r="C69" s="37"/>
-      <c r="D69" s="37"/>
-      <c r="E69" s="37"/>
-      <c r="F69" s="37"/>
-      <c r="G69" s="37"/>
-      <c r="H69" s="37"/>
-      <c r="I69" s="37"/>
-      <c r="J69" s="37"/>
+      <c r="B69" s="44"/>
+      <c r="C69" s="44"/>
+      <c r="D69" s="44"/>
+      <c r="E69" s="44"/>
+      <c r="F69" s="44"/>
+      <c r="G69" s="44"/>
+      <c r="H69" s="44"/>
+      <c r="I69" s="44"/>
+      <c r="J69" s="44"/>
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="37"/>
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="37"/>
-      <c r="G70" s="37"/>
-      <c r="H70" s="37"/>
-      <c r="I70" s="37"/>
-      <c r="J70" s="37"/>
+      <c r="B70" s="44"/>
+      <c r="C70" s="44"/>
+      <c r="D70" s="44"/>
+      <c r="E70" s="44"/>
+      <c r="F70" s="44"/>
+      <c r="G70" s="44"/>
+      <c r="H70" s="44"/>
+      <c r="I70" s="44"/>
+      <c r="J70" s="44"/>
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="37"/>
-      <c r="C71" s="37"/>
-      <c r="D71" s="37"/>
-      <c r="E71" s="37"/>
-      <c r="F71" s="37"/>
-      <c r="G71" s="37"/>
-      <c r="H71" s="37"/>
-      <c r="I71" s="37"/>
-      <c r="J71" s="37"/>
+      <c r="B71" s="44"/>
+      <c r="C71" s="44"/>
+      <c r="D71" s="44"/>
+      <c r="E71" s="44"/>
+      <c r="F71" s="44"/>
+      <c r="G71" s="44"/>
+      <c r="H71" s="44"/>
+      <c r="I71" s="44"/>
+      <c r="J71" s="44"/>
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="37"/>
-      <c r="C72" s="37"/>
-      <c r="D72" s="37"/>
-      <c r="E72" s="37"/>
-      <c r="F72" s="37"/>
-      <c r="G72" s="37"/>
-      <c r="H72" s="37"/>
-      <c r="I72" s="37"/>
-      <c r="J72" s="37"/>
+      <c r="B72" s="44"/>
+      <c r="C72" s="44"/>
+      <c r="D72" s="44"/>
+      <c r="E72" s="44"/>
+      <c r="F72" s="44"/>
+      <c r="G72" s="44"/>
+      <c r="H72" s="44"/>
+      <c r="I72" s="44"/>
+      <c r="J72" s="44"/>
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="37"/>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
-      <c r="J73" s="37"/>
+      <c r="B73" s="44"/>
+      <c r="C73" s="44"/>
+      <c r="D73" s="44"/>
+      <c r="E73" s="44"/>
+      <c r="F73" s="44"/>
+      <c r="G73" s="44"/>
+      <c r="H73" s="44"/>
+      <c r="I73" s="44"/>
+      <c r="J73" s="44"/>
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="37"/>
-      <c r="C74" s="37"/>
-      <c r="D74" s="37"/>
-      <c r="E74" s="37"/>
-      <c r="F74" s="37"/>
-      <c r="G74" s="37"/>
-      <c r="H74" s="37"/>
-      <c r="I74" s="37"/>
-      <c r="J74" s="37"/>
+      <c r="B74" s="44"/>
+      <c r="C74" s="44"/>
+      <c r="D74" s="44"/>
+      <c r="E74" s="44"/>
+      <c r="F74" s="44"/>
+      <c r="G74" s="44"/>
+      <c r="H74" s="44"/>
+      <c r="I74" s="44"/>
+      <c r="J74" s="44"/>
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="37"/>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="37"/>
-      <c r="J75" s="37"/>
+      <c r="B75" s="44"/>
+      <c r="C75" s="44"/>
+      <c r="D75" s="44"/>
+      <c r="E75" s="44"/>
+      <c r="F75" s="44"/>
+      <c r="G75" s="44"/>
+      <c r="H75" s="44"/>
+      <c r="I75" s="44"/>
+      <c r="J75" s="44"/>
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="37"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="37"/>
-      <c r="G76" s="37"/>
-      <c r="H76" s="37"/>
-      <c r="I76" s="37"/>
-      <c r="J76" s="37"/>
+      <c r="B76" s="44"/>
+      <c r="C76" s="44"/>
+      <c r="D76" s="44"/>
+      <c r="E76" s="44"/>
+      <c r="F76" s="44"/>
+      <c r="G76" s="44"/>
+      <c r="H76" s="44"/>
+      <c r="I76" s="44"/>
+      <c r="J76" s="44"/>
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="37"/>
-      <c r="C77" s="37"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="37"/>
-      <c r="F77" s="37"/>
-      <c r="G77" s="37"/>
-      <c r="H77" s="37"/>
-      <c r="I77" s="37"/>
-      <c r="J77" s="37"/>
+      <c r="B77" s="44"/>
+      <c r="C77" s="44"/>
+      <c r="D77" s="44"/>
+      <c r="E77" s="44"/>
+      <c r="F77" s="44"/>
+      <c r="G77" s="44"/>
+      <c r="H77" s="44"/>
+      <c r="I77" s="44"/>
+      <c r="J77" s="44"/>
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="37"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="37"/>
-      <c r="E78" s="37"/>
-      <c r="F78" s="37"/>
-      <c r="G78" s="37"/>
-      <c r="H78" s="37"/>
-      <c r="I78" s="37"/>
-      <c r="J78" s="37"/>
+      <c r="B78" s="44"/>
+      <c r="C78" s="44"/>
+      <c r="D78" s="44"/>
+      <c r="E78" s="44"/>
+      <c r="F78" s="44"/>
+      <c r="G78" s="44"/>
+      <c r="H78" s="44"/>
+      <c r="I78" s="44"/>
+      <c r="J78" s="44"/>
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="37"/>
-      <c r="C79" s="37"/>
-      <c r="D79" s="37"/>
-      <c r="E79" s="37"/>
-      <c r="F79" s="37"/>
-      <c r="G79" s="37"/>
-      <c r="H79" s="37"/>
-      <c r="I79" s="37"/>
-      <c r="J79" s="37"/>
+      <c r="B79" s="44"/>
+      <c r="C79" s="44"/>
+      <c r="D79" s="44"/>
+      <c r="E79" s="44"/>
+      <c r="F79" s="44"/>
+      <c r="G79" s="44"/>
+      <c r="H79" s="44"/>
+      <c r="I79" s="44"/>
+      <c r="J79" s="44"/>
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="37"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="37"/>
-      <c r="E80" s="37"/>
-      <c r="F80" s="37"/>
-      <c r="G80" s="37"/>
-      <c r="H80" s="37"/>
-      <c r="I80" s="37"/>
-      <c r="J80" s="37"/>
+      <c r="B80" s="44"/>
+      <c r="C80" s="44"/>
+      <c r="D80" s="44"/>
+      <c r="E80" s="44"/>
+      <c r="F80" s="44"/>
+      <c r="G80" s="44"/>
+      <c r="H80" s="44"/>
+      <c r="I80" s="44"/>
+      <c r="J80" s="44"/>
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="37"/>
-      <c r="C81" s="37"/>
-      <c r="D81" s="37"/>
-      <c r="E81" s="37"/>
-      <c r="F81" s="37"/>
-      <c r="G81" s="37"/>
-      <c r="H81" s="37"/>
-      <c r="I81" s="37"/>
-      <c r="J81" s="37"/>
+      <c r="B81" s="44"/>
+      <c r="C81" s="44"/>
+      <c r="D81" s="44"/>
+      <c r="E81" s="44"/>
+      <c r="F81" s="44"/>
+      <c r="G81" s="44"/>
+      <c r="H81" s="44"/>
+      <c r="I81" s="44"/>
+      <c r="J81" s="44"/>
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="37"/>
-      <c r="C82" s="37"/>
-      <c r="D82" s="37"/>
-      <c r="E82" s="37"/>
-      <c r="F82" s="37"/>
-      <c r="G82" s="37"/>
-      <c r="H82" s="37"/>
-      <c r="I82" s="37"/>
-      <c r="J82" s="37"/>
+      <c r="B82" s="44"/>
+      <c r="C82" s="44"/>
+      <c r="D82" s="44"/>
+      <c r="E82" s="44"/>
+      <c r="F82" s="44"/>
+      <c r="G82" s="44"/>
+      <c r="H82" s="44"/>
+      <c r="I82" s="44"/>
+      <c r="J82" s="44"/>
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="37"/>
-      <c r="C83" s="37"/>
-      <c r="D83" s="37"/>
-      <c r="E83" s="37"/>
-      <c r="F83" s="37"/>
-      <c r="G83" s="37"/>
-      <c r="H83" s="37"/>
-      <c r="I83" s="37"/>
-      <c r="J83" s="37"/>
+      <c r="B83" s="44"/>
+      <c r="C83" s="44"/>
+      <c r="D83" s="44"/>
+      <c r="E83" s="44"/>
+      <c r="F83" s="44"/>
+      <c r="G83" s="44"/>
+      <c r="H83" s="44"/>
+      <c r="I83" s="44"/>
+      <c r="J83" s="44"/>
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="37"/>
-      <c r="C84" s="37"/>
-      <c r="D84" s="37"/>
-      <c r="E84" s="37"/>
-      <c r="F84" s="37"/>
-      <c r="G84" s="37"/>
-      <c r="H84" s="37"/>
-      <c r="I84" s="37"/>
-      <c r="J84" s="37"/>
+      <c r="B84" s="44"/>
+      <c r="C84" s="44"/>
+      <c r="D84" s="44"/>
+      <c r="E84" s="44"/>
+      <c r="F84" s="44"/>
+      <c r="G84" s="44"/>
+      <c r="H84" s="44"/>
+      <c r="I84" s="44"/>
+      <c r="J84" s="44"/>
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B85" s="37"/>
-      <c r="C85" s="37"/>
-      <c r="D85" s="37"/>
-      <c r="E85" s="37"/>
-      <c r="F85" s="37"/>
-      <c r="G85" s="37"/>
-      <c r="H85" s="37"/>
-      <c r="I85" s="37"/>
-      <c r="J85" s="37"/>
+      <c r="B85" s="44"/>
+      <c r="C85" s="44"/>
+      <c r="D85" s="44"/>
+      <c r="E85" s="44"/>
+      <c r="F85" s="44"/>
+      <c r="G85" s="44"/>
+      <c r="H85" s="44"/>
+      <c r="I85" s="44"/>
+      <c r="J85" s="44"/>
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="37"/>
-      <c r="C86" s="37"/>
-      <c r="D86" s="37"/>
-      <c r="E86" s="37"/>
-      <c r="F86" s="37"/>
-      <c r="G86" s="37"/>
-      <c r="H86" s="37"/>
-      <c r="I86" s="37"/>
-      <c r="J86" s="37"/>
+      <c r="B86" s="44"/>
+      <c r="C86" s="44"/>
+      <c r="D86" s="44"/>
+      <c r="E86" s="44"/>
+      <c r="F86" s="44"/>
+      <c r="G86" s="44"/>
+      <c r="H86" s="44"/>
+      <c r="I86" s="44"/>
+      <c r="J86" s="44"/>
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B87" s="37"/>
-      <c r="C87" s="37"/>
-      <c r="D87" s="37"/>
-      <c r="E87" s="37"/>
-      <c r="F87" s="37"/>
-      <c r="G87" s="37"/>
-      <c r="H87" s="37"/>
-      <c r="I87" s="37"/>
-      <c r="J87" s="37"/>
+      <c r="B87" s="44"/>
+      <c r="C87" s="44"/>
+      <c r="D87" s="44"/>
+      <c r="E87" s="44"/>
+      <c r="F87" s="44"/>
+      <c r="G87" s="44"/>
+      <c r="H87" s="44"/>
+      <c r="I87" s="44"/>
+      <c r="J87" s="44"/>
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B88" s="37"/>
-      <c r="C88" s="37"/>
-      <c r="D88" s="37"/>
-      <c r="E88" s="37"/>
-      <c r="F88" s="37"/>
-      <c r="G88" s="37"/>
-      <c r="H88" s="37"/>
-      <c r="I88" s="37"/>
-      <c r="J88" s="37"/>
+      <c r="B88" s="44"/>
+      <c r="C88" s="44"/>
+      <c r="D88" s="44"/>
+      <c r="E88" s="44"/>
+      <c r="F88" s="44"/>
+      <c r="G88" s="44"/>
+      <c r="H88" s="44"/>
+      <c r="I88" s="44"/>
+      <c r="J88" s="44"/>
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="90" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="36" t="s">
+      <c r="B90" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="C90" s="37"/>
-      <c r="D90" s="37"/>
-      <c r="E90" s="37"/>
-      <c r="F90" s="37"/>
-      <c r="G90" s="37"/>
-      <c r="H90" s="37"/>
-      <c r="I90" s="37"/>
-      <c r="J90" s="37"/>
+      <c r="C90" s="44"/>
+      <c r="D90" s="44"/>
+      <c r="E90" s="44"/>
+      <c r="F90" s="44"/>
+      <c r="G90" s="44"/>
+      <c r="H90" s="44"/>
+      <c r="I90" s="44"/>
+      <c r="J90" s="44"/>
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="37"/>
-      <c r="C91" s="37"/>
-      <c r="D91" s="37"/>
-      <c r="E91" s="37"/>
-      <c r="F91" s="37"/>
-      <c r="G91" s="37"/>
-      <c r="H91" s="37"/>
-      <c r="I91" s="37"/>
-      <c r="J91" s="37"/>
+      <c r="B91" s="44"/>
+      <c r="C91" s="44"/>
+      <c r="D91" s="44"/>
+      <c r="E91" s="44"/>
+      <c r="F91" s="44"/>
+      <c r="G91" s="44"/>
+      <c r="H91" s="44"/>
+      <c r="I91" s="44"/>
+      <c r="J91" s="44"/>
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B92" s="37"/>
-      <c r="C92" s="37"/>
-      <c r="D92" s="37"/>
-      <c r="E92" s="37"/>
-      <c r="F92" s="37"/>
-      <c r="G92" s="37"/>
-      <c r="H92" s="37"/>
-      <c r="I92" s="37"/>
-      <c r="J92" s="37"/>
+      <c r="B92" s="44"/>
+      <c r="C92" s="44"/>
+      <c r="D92" s="44"/>
+      <c r="E92" s="44"/>
+      <c r="F92" s="44"/>
+      <c r="G92" s="44"/>
+      <c r="H92" s="44"/>
+      <c r="I92" s="44"/>
+      <c r="J92" s="44"/>
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B93" s="37"/>
-      <c r="C93" s="37"/>
-      <c r="D93" s="37"/>
-      <c r="E93" s="37"/>
-      <c r="F93" s="37"/>
-      <c r="G93" s="37"/>
-      <c r="H93" s="37"/>
-      <c r="I93" s="37"/>
-      <c r="J93" s="37"/>
+      <c r="B93" s="44"/>
+      <c r="C93" s="44"/>
+      <c r="D93" s="44"/>
+      <c r="E93" s="44"/>
+      <c r="F93" s="44"/>
+      <c r="G93" s="44"/>
+      <c r="H93" s="44"/>
+      <c r="I93" s="44"/>
+      <c r="J93" s="44"/>
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="37"/>
-      <c r="C94" s="37"/>
-      <c r="D94" s="37"/>
-      <c r="E94" s="37"/>
-      <c r="F94" s="37"/>
-      <c r="G94" s="37"/>
-      <c r="H94" s="37"/>
-      <c r="I94" s="37"/>
-      <c r="J94" s="37"/>
+      <c r="B94" s="44"/>
+      <c r="C94" s="44"/>
+      <c r="D94" s="44"/>
+      <c r="E94" s="44"/>
+      <c r="F94" s="44"/>
+      <c r="G94" s="44"/>
+      <c r="H94" s="44"/>
+      <c r="I94" s="44"/>
+      <c r="J94" s="44"/>
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B95" s="37"/>
-      <c r="C95" s="37"/>
-      <c r="D95" s="37"/>
-      <c r="E95" s="37"/>
-      <c r="F95" s="37"/>
-      <c r="G95" s="37"/>
-      <c r="H95" s="37"/>
-      <c r="I95" s="37"/>
-      <c r="J95" s="37"/>
+      <c r="B95" s="44"/>
+      <c r="C95" s="44"/>
+      <c r="D95" s="44"/>
+      <c r="E95" s="44"/>
+      <c r="F95" s="44"/>
+      <c r="G95" s="44"/>
+      <c r="H95" s="44"/>
+      <c r="I95" s="44"/>
+      <c r="J95" s="44"/>
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B96" s="37"/>
-      <c r="C96" s="37"/>
-      <c r="D96" s="37"/>
-      <c r="E96" s="37"/>
-      <c r="F96" s="37"/>
-      <c r="G96" s="37"/>
-      <c r="H96" s="37"/>
-      <c r="I96" s="37"/>
-      <c r="J96" s="37"/>
+      <c r="B96" s="44"/>
+      <c r="C96" s="44"/>
+      <c r="D96" s="44"/>
+      <c r="E96" s="44"/>
+      <c r="F96" s="44"/>
+      <c r="G96" s="44"/>
+      <c r="H96" s="44"/>
+      <c r="I96" s="44"/>
+      <c r="J96" s="44"/>
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B97" s="37"/>
-      <c r="C97" s="37"/>
-      <c r="D97" s="37"/>
-      <c r="E97" s="37"/>
-      <c r="F97" s="37"/>
-      <c r="G97" s="37"/>
-      <c r="H97" s="37"/>
-      <c r="I97" s="37"/>
-      <c r="J97" s="37"/>
+      <c r="B97" s="44"/>
+      <c r="C97" s="44"/>
+      <c r="D97" s="44"/>
+      <c r="E97" s="44"/>
+      <c r="F97" s="44"/>
+      <c r="G97" s="44"/>
+      <c r="H97" s="44"/>
+      <c r="I97" s="44"/>
+      <c r="J97" s="44"/>
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="37"/>
-      <c r="C98" s="37"/>
-      <c r="D98" s="37"/>
-      <c r="E98" s="37"/>
-      <c r="F98" s="37"/>
-      <c r="G98" s="37"/>
-      <c r="H98" s="37"/>
-      <c r="I98" s="37"/>
-      <c r="J98" s="37"/>
+      <c r="B98" s="44"/>
+      <c r="C98" s="44"/>
+      <c r="D98" s="44"/>
+      <c r="E98" s="44"/>
+      <c r="F98" s="44"/>
+      <c r="G98" s="44"/>
+      <c r="H98" s="44"/>
+      <c r="I98" s="44"/>
+      <c r="J98" s="44"/>
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B99" s="37"/>
-      <c r="C99" s="37"/>
-      <c r="D99" s="37"/>
-      <c r="E99" s="37"/>
-      <c r="F99" s="37"/>
-      <c r="G99" s="37"/>
-      <c r="H99" s="37"/>
-      <c r="I99" s="37"/>
-      <c r="J99" s="37"/>
+      <c r="B99" s="44"/>
+      <c r="C99" s="44"/>
+      <c r="D99" s="44"/>
+      <c r="E99" s="44"/>
+      <c r="F99" s="44"/>
+      <c r="G99" s="44"/>
+      <c r="H99" s="44"/>
+      <c r="I99" s="44"/>
+      <c r="J99" s="44"/>
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B100" s="37"/>
-      <c r="C100" s="37"/>
-      <c r="D100" s="37"/>
-      <c r="E100" s="37"/>
-      <c r="F100" s="37"/>
-      <c r="G100" s="37"/>
-      <c r="H100" s="37"/>
-      <c r="I100" s="37"/>
-      <c r="J100" s="37"/>
+      <c r="B100" s="44"/>
+      <c r="C100" s="44"/>
+      <c r="D100" s="44"/>
+      <c r="E100" s="44"/>
+      <c r="F100" s="44"/>
+      <c r="G100" s="44"/>
+      <c r="H100" s="44"/>
+      <c r="I100" s="44"/>
+      <c r="J100" s="44"/>
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B101" s="37"/>
-      <c r="C101" s="37"/>
-      <c r="D101" s="37"/>
-      <c r="E101" s="37"/>
-      <c r="F101" s="37"/>
-      <c r="G101" s="37"/>
-      <c r="H101" s="37"/>
-      <c r="I101" s="37"/>
-      <c r="J101" s="37"/>
+      <c r="B101" s="44"/>
+      <c r="C101" s="44"/>
+      <c r="D101" s="44"/>
+      <c r="E101" s="44"/>
+      <c r="F101" s="44"/>
+      <c r="G101" s="44"/>
+      <c r="H101" s="44"/>
+      <c r="I101" s="44"/>
+      <c r="J101" s="44"/>
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B102" s="37"/>
-      <c r="C102" s="37"/>
-      <c r="D102" s="37"/>
-      <c r="E102" s="37"/>
-      <c r="F102" s="37"/>
-      <c r="G102" s="37"/>
-      <c r="H102" s="37"/>
-      <c r="I102" s="37"/>
-      <c r="J102" s="37"/>
+      <c r="B102" s="44"/>
+      <c r="C102" s="44"/>
+      <c r="D102" s="44"/>
+      <c r="E102" s="44"/>
+      <c r="F102" s="44"/>
+      <c r="G102" s="44"/>
+      <c r="H102" s="44"/>
+      <c r="I102" s="44"/>
+      <c r="J102" s="44"/>
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B103" s="37"/>
-      <c r="C103" s="37"/>
-      <c r="D103" s="37"/>
-      <c r="E103" s="37"/>
-      <c r="F103" s="37"/>
-      <c r="G103" s="37"/>
-      <c r="H103" s="37"/>
-      <c r="I103" s="37"/>
-      <c r="J103" s="37"/>
+      <c r="B103" s="44"/>
+      <c r="C103" s="44"/>
+      <c r="D103" s="44"/>
+      <c r="E103" s="44"/>
+      <c r="F103" s="44"/>
+      <c r="G103" s="44"/>
+      <c r="H103" s="44"/>
+      <c r="I103" s="44"/>
+      <c r="J103" s="44"/>
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B104" s="37"/>
-      <c r="C104" s="37"/>
-      <c r="D104" s="37"/>
-      <c r="E104" s="37"/>
-      <c r="F104" s="37"/>
-      <c r="G104" s="37"/>
-      <c r="H104" s="37"/>
-      <c r="I104" s="37"/>
-      <c r="J104" s="37"/>
+      <c r="B104" s="44"/>
+      <c r="C104" s="44"/>
+      <c r="D104" s="44"/>
+      <c r="E104" s="44"/>
+      <c r="F104" s="44"/>
+      <c r="G104" s="44"/>
+      <c r="H104" s="44"/>
+      <c r="I104" s="44"/>
+      <c r="J104" s="44"/>
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B105" s="37"/>
-      <c r="C105" s="37"/>
-      <c r="D105" s="37"/>
-      <c r="E105" s="37"/>
-      <c r="F105" s="37"/>
-      <c r="G105" s="37"/>
-      <c r="H105" s="37"/>
-      <c r="I105" s="37"/>
-      <c r="J105" s="37"/>
+      <c r="B105" s="44"/>
+      <c r="C105" s="44"/>
+      <c r="D105" s="44"/>
+      <c r="E105" s="44"/>
+      <c r="F105" s="44"/>
+      <c r="G105" s="44"/>
+      <c r="H105" s="44"/>
+      <c r="I105" s="44"/>
+      <c r="J105" s="44"/>
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B106" s="37"/>
-      <c r="C106" s="37"/>
-      <c r="D106" s="37"/>
-      <c r="E106" s="37"/>
-      <c r="F106" s="37"/>
-      <c r="G106" s="37"/>
-      <c r="H106" s="37"/>
-      <c r="I106" s="37"/>
-      <c r="J106" s="37"/>
+      <c r="B106" s="44"/>
+      <c r="C106" s="44"/>
+      <c r="D106" s="44"/>
+      <c r="E106" s="44"/>
+      <c r="F106" s="44"/>
+      <c r="G106" s="44"/>
+      <c r="H106" s="44"/>
+      <c r="I106" s="44"/>
+      <c r="J106" s="44"/>
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B107" s="37"/>
-      <c r="C107" s="37"/>
-      <c r="D107" s="37"/>
-      <c r="E107" s="37"/>
-      <c r="F107" s="37"/>
-      <c r="G107" s="37"/>
-      <c r="H107" s="37"/>
-      <c r="I107" s="37"/>
-      <c r="J107" s="37"/>
+      <c r="B107" s="44"/>
+      <c r="C107" s="44"/>
+      <c r="D107" s="44"/>
+      <c r="E107" s="44"/>
+      <c r="F107" s="44"/>
+      <c r="G107" s="44"/>
+      <c r="H107" s="44"/>
+      <c r="I107" s="44"/>
+      <c r="J107" s="44"/>
     </row>
     <row r="108" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B108" s="37"/>
-      <c r="C108" s="37"/>
-      <c r="D108" s="37"/>
-      <c r="E108" s="37"/>
-      <c r="F108" s="37"/>
-      <c r="G108" s="37"/>
-      <c r="H108" s="37"/>
-      <c r="I108" s="37"/>
-      <c r="J108" s="37"/>
+      <c r="B108" s="44"/>
+      <c r="C108" s="44"/>
+      <c r="D108" s="44"/>
+      <c r="E108" s="44"/>
+      <c r="F108" s="44"/>
+      <c r="G108" s="44"/>
+      <c r="H108" s="44"/>
+      <c r="I108" s="44"/>
+      <c r="J108" s="44"/>
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B109" s="37"/>
-      <c r="C109" s="37"/>
-      <c r="D109" s="37"/>
-      <c r="E109" s="37"/>
-      <c r="F109" s="37"/>
-      <c r="G109" s="37"/>
-      <c r="H109" s="37"/>
-      <c r="I109" s="37"/>
-      <c r="J109" s="37"/>
+      <c r="B109" s="44"/>
+      <c r="C109" s="44"/>
+      <c r="D109" s="44"/>
+      <c r="E109" s="44"/>
+      <c r="F109" s="44"/>
+      <c r="G109" s="44"/>
+      <c r="H109" s="44"/>
+      <c r="I109" s="44"/>
+      <c r="J109" s="44"/>
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B110" s="37"/>
-      <c r="C110" s="37"/>
-      <c r="D110" s="37"/>
-      <c r="E110" s="37"/>
-      <c r="F110" s="37"/>
-      <c r="G110" s="37"/>
-      <c r="H110" s="37"/>
-      <c r="I110" s="37"/>
-      <c r="J110" s="37"/>
+      <c r="B110" s="44"/>
+      <c r="C110" s="44"/>
+      <c r="D110" s="44"/>
+      <c r="E110" s="44"/>
+      <c r="F110" s="44"/>
+      <c r="G110" s="44"/>
+      <c r="H110" s="44"/>
+      <c r="I110" s="44"/>
+      <c r="J110" s="44"/>
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B111" s="37"/>
-      <c r="C111" s="37"/>
-      <c r="D111" s="37"/>
-      <c r="E111" s="37"/>
-      <c r="F111" s="37"/>
-      <c r="G111" s="37"/>
-      <c r="H111" s="37"/>
-      <c r="I111" s="37"/>
-      <c r="J111" s="37"/>
+      <c r="B111" s="44"/>
+      <c r="C111" s="44"/>
+      <c r="D111" s="44"/>
+      <c r="E111" s="44"/>
+      <c r="F111" s="44"/>
+      <c r="G111" s="44"/>
+      <c r="H111" s="44"/>
+      <c r="I111" s="44"/>
+      <c r="J111" s="44"/>
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="37"/>
-      <c r="C112" s="37"/>
-      <c r="D112" s="37"/>
-      <c r="E112" s="37"/>
-      <c r="F112" s="37"/>
-      <c r="G112" s="37"/>
-      <c r="H112" s="37"/>
-      <c r="I112" s="37"/>
-      <c r="J112" s="37"/>
+      <c r="B112" s="44"/>
+      <c r="C112" s="44"/>
+      <c r="D112" s="44"/>
+      <c r="E112" s="44"/>
+      <c r="F112" s="44"/>
+      <c r="G112" s="44"/>
+      <c r="H112" s="44"/>
+      <c r="I112" s="44"/>
+      <c r="J112" s="44"/>
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B113" s="37"/>
-      <c r="C113" s="37"/>
-      <c r="D113" s="37"/>
-      <c r="E113" s="37"/>
-      <c r="F113" s="37"/>
-      <c r="G113" s="37"/>
-      <c r="H113" s="37"/>
-      <c r="I113" s="37"/>
-      <c r="J113" s="37"/>
+      <c r="B113" s="44"/>
+      <c r="C113" s="44"/>
+      <c r="D113" s="44"/>
+      <c r="E113" s="44"/>
+      <c r="F113" s="44"/>
+      <c r="G113" s="44"/>
+      <c r="H113" s="44"/>
+      <c r="I113" s="44"/>
+      <c r="J113" s="44"/>
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B114" s="37"/>
-      <c r="C114" s="37"/>
-      <c r="D114" s="37"/>
-      <c r="E114" s="37"/>
-      <c r="F114" s="37"/>
-      <c r="G114" s="37"/>
-      <c r="H114" s="37"/>
-      <c r="I114" s="37"/>
-      <c r="J114" s="37"/>
+      <c r="B114" s="44"/>
+      <c r="C114" s="44"/>
+      <c r="D114" s="44"/>
+      <c r="E114" s="44"/>
+      <c r="F114" s="44"/>
+      <c r="G114" s="44"/>
+      <c r="H114" s="44"/>
+      <c r="I114" s="44"/>
+      <c r="J114" s="44"/>
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B115" s="37"/>
-      <c r="C115" s="37"/>
-      <c r="D115" s="37"/>
-      <c r="E115" s="37"/>
-      <c r="F115" s="37"/>
-      <c r="G115" s="37"/>
-      <c r="H115" s="37"/>
-      <c r="I115" s="37"/>
-      <c r="J115" s="37"/>
+      <c r="B115" s="44"/>
+      <c r="C115" s="44"/>
+      <c r="D115" s="44"/>
+      <c r="E115" s="44"/>
+      <c r="F115" s="44"/>
+      <c r="G115" s="44"/>
+      <c r="H115" s="44"/>
+      <c r="I115" s="44"/>
+      <c r="J115" s="44"/>
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B116" s="37"/>
-      <c r="C116" s="37"/>
-      <c r="D116" s="37"/>
-      <c r="E116" s="37"/>
-      <c r="F116" s="37"/>
-      <c r="G116" s="37"/>
-      <c r="H116" s="37"/>
-      <c r="I116" s="37"/>
-      <c r="J116" s="37"/>
+      <c r="B116" s="44"/>
+      <c r="C116" s="44"/>
+      <c r="D116" s="44"/>
+      <c r="E116" s="44"/>
+      <c r="F116" s="44"/>
+      <c r="G116" s="44"/>
+      <c r="H116" s="44"/>
+      <c r="I116" s="44"/>
+      <c r="J116" s="44"/>
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="118" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B118" s="36" t="s">
+      <c r="B118" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="C118" s="37"/>
-      <c r="D118" s="37"/>
-      <c r="E118" s="37"/>
-      <c r="F118" s="37"/>
-      <c r="G118" s="37"/>
-      <c r="H118" s="37"/>
-      <c r="I118" s="37"/>
-      <c r="J118" s="37"/>
+      <c r="C118" s="44"/>
+      <c r="D118" s="44"/>
+      <c r="E118" s="44"/>
+      <c r="F118" s="44"/>
+      <c r="G118" s="44"/>
+      <c r="H118" s="44"/>
+      <c r="I118" s="44"/>
+      <c r="J118" s="44"/>
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B119" s="37"/>
-      <c r="C119" s="37"/>
-      <c r="D119" s="37"/>
-      <c r="E119" s="37"/>
-      <c r="F119" s="37"/>
-      <c r="G119" s="37"/>
-      <c r="H119" s="37"/>
-      <c r="I119" s="37"/>
-      <c r="J119" s="37"/>
+      <c r="B119" s="44"/>
+      <c r="C119" s="44"/>
+      <c r="D119" s="44"/>
+      <c r="E119" s="44"/>
+      <c r="F119" s="44"/>
+      <c r="G119" s="44"/>
+      <c r="H119" s="44"/>
+      <c r="I119" s="44"/>
+      <c r="J119" s="44"/>
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="37"/>
-      <c r="C120" s="37"/>
-      <c r="D120" s="37"/>
-      <c r="E120" s="37"/>
-      <c r="F120" s="37"/>
-      <c r="G120" s="37"/>
-      <c r="H120" s="37"/>
-      <c r="I120" s="37"/>
-      <c r="J120" s="37"/>
+      <c r="B120" s="44"/>
+      <c r="C120" s="44"/>
+      <c r="D120" s="44"/>
+      <c r="E120" s="44"/>
+      <c r="F120" s="44"/>
+      <c r="G120" s="44"/>
+      <c r="H120" s="44"/>
+      <c r="I120" s="44"/>
+      <c r="J120" s="44"/>
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="37"/>
-      <c r="C121" s="37"/>
-      <c r="D121" s="37"/>
-      <c r="E121" s="37"/>
-      <c r="F121" s="37"/>
-      <c r="G121" s="37"/>
-      <c r="H121" s="37"/>
-      <c r="I121" s="37"/>
-      <c r="J121" s="37"/>
+      <c r="B121" s="44"/>
+      <c r="C121" s="44"/>
+      <c r="D121" s="44"/>
+      <c r="E121" s="44"/>
+      <c r="F121" s="44"/>
+      <c r="G121" s="44"/>
+      <c r="H121" s="44"/>
+      <c r="I121" s="44"/>
+      <c r="J121" s="44"/>
     </row>
     <row r="122" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="37"/>
-      <c r="C122" s="37"/>
-      <c r="D122" s="37"/>
-      <c r="E122" s="37"/>
-      <c r="F122" s="37"/>
-      <c r="G122" s="37"/>
-      <c r="H122" s="37"/>
-      <c r="I122" s="37"/>
-      <c r="J122" s="37"/>
+      <c r="B122" s="44"/>
+      <c r="C122" s="44"/>
+      <c r="D122" s="44"/>
+      <c r="E122" s="44"/>
+      <c r="F122" s="44"/>
+      <c r="G122" s="44"/>
+      <c r="H122" s="44"/>
+      <c r="I122" s="44"/>
+      <c r="J122" s="44"/>
     </row>
     <row r="123" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="37"/>
-      <c r="C123" s="37"/>
-      <c r="D123" s="37"/>
-      <c r="E123" s="37"/>
-      <c r="F123" s="37"/>
-      <c r="G123" s="37"/>
-      <c r="H123" s="37"/>
-      <c r="I123" s="37"/>
-      <c r="J123" s="37"/>
+      <c r="B123" s="44"/>
+      <c r="C123" s="44"/>
+      <c r="D123" s="44"/>
+      <c r="E123" s="44"/>
+      <c r="F123" s="44"/>
+      <c r="G123" s="44"/>
+      <c r="H123" s="44"/>
+      <c r="I123" s="44"/>
+      <c r="J123" s="44"/>
     </row>
     <row r="124" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="37"/>
-      <c r="C124" s="37"/>
-      <c r="D124" s="37"/>
-      <c r="E124" s="37"/>
-      <c r="F124" s="37"/>
-      <c r="G124" s="37"/>
-      <c r="H124" s="37"/>
-      <c r="I124" s="37"/>
-      <c r="J124" s="37"/>
+      <c r="B124" s="44"/>
+      <c r="C124" s="44"/>
+      <c r="D124" s="44"/>
+      <c r="E124" s="44"/>
+      <c r="F124" s="44"/>
+      <c r="G124" s="44"/>
+      <c r="H124" s="44"/>
+      <c r="I124" s="44"/>
+      <c r="J124" s="44"/>
     </row>
     <row r="125" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="37"/>
-      <c r="C125" s="37"/>
-      <c r="D125" s="37"/>
-      <c r="E125" s="37"/>
-      <c r="F125" s="37"/>
-      <c r="G125" s="37"/>
-      <c r="H125" s="37"/>
-      <c r="I125" s="37"/>
-      <c r="J125" s="37"/>
+      <c r="B125" s="44"/>
+      <c r="C125" s="44"/>
+      <c r="D125" s="44"/>
+      <c r="E125" s="44"/>
+      <c r="F125" s="44"/>
+      <c r="G125" s="44"/>
+      <c r="H125" s="44"/>
+      <c r="I125" s="44"/>
+      <c r="J125" s="44"/>
     </row>
     <row r="126" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B126" s="37"/>
-      <c r="C126" s="37"/>
-      <c r="D126" s="37"/>
-      <c r="E126" s="37"/>
-      <c r="F126" s="37"/>
-      <c r="G126" s="37"/>
-      <c r="H126" s="37"/>
-      <c r="I126" s="37"/>
-      <c r="J126" s="37"/>
+      <c r="B126" s="44"/>
+      <c r="C126" s="44"/>
+      <c r="D126" s="44"/>
+      <c r="E126" s="44"/>
+      <c r="F126" s="44"/>
+      <c r="G126" s="44"/>
+      <c r="H126" s="44"/>
+      <c r="I126" s="44"/>
+      <c r="J126" s="44"/>
     </row>
     <row r="127" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B127" s="37"/>
-      <c r="C127" s="37"/>
-      <c r="D127" s="37"/>
-      <c r="E127" s="37"/>
-      <c r="F127" s="37"/>
-      <c r="G127" s="37"/>
-      <c r="H127" s="37"/>
-      <c r="I127" s="37"/>
-      <c r="J127" s="37"/>
+      <c r="B127" s="44"/>
+      <c r="C127" s="44"/>
+      <c r="D127" s="44"/>
+      <c r="E127" s="44"/>
+      <c r="F127" s="44"/>
+      <c r="G127" s="44"/>
+      <c r="H127" s="44"/>
+      <c r="I127" s="44"/>
+      <c r="J127" s="44"/>
     </row>
     <row r="128" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B128" s="37"/>
-      <c r="C128" s="37"/>
-      <c r="D128" s="37"/>
-      <c r="E128" s="37"/>
-      <c r="F128" s="37"/>
-      <c r="G128" s="37"/>
-      <c r="H128" s="37"/>
-      <c r="I128" s="37"/>
-      <c r="J128" s="37"/>
+      <c r="B128" s="44"/>
+      <c r="C128" s="44"/>
+      <c r="D128" s="44"/>
+      <c r="E128" s="44"/>
+      <c r="F128" s="44"/>
+      <c r="G128" s="44"/>
+      <c r="H128" s="44"/>
+      <c r="I128" s="44"/>
+      <c r="J128" s="44"/>
     </row>
     <row r="129" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B129" s="37"/>
-      <c r="C129" s="37"/>
-      <c r="D129" s="37"/>
-      <c r="E129" s="37"/>
-      <c r="F129" s="37"/>
-      <c r="G129" s="37"/>
-      <c r="H129" s="37"/>
-      <c r="I129" s="37"/>
-      <c r="J129" s="37"/>
+      <c r="B129" s="44"/>
+      <c r="C129" s="44"/>
+      <c r="D129" s="44"/>
+      <c r="E129" s="44"/>
+      <c r="F129" s="44"/>
+      <c r="G129" s="44"/>
+      <c r="H129" s="44"/>
+      <c r="I129" s="44"/>
+      <c r="J129" s="44"/>
     </row>
     <row r="130" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B130" s="37"/>
-      <c r="C130" s="37"/>
-      <c r="D130" s="37"/>
-      <c r="E130" s="37"/>
-      <c r="F130" s="37"/>
-      <c r="G130" s="37"/>
-      <c r="H130" s="37"/>
-      <c r="I130" s="37"/>
-      <c r="J130" s="37"/>
+      <c r="B130" s="44"/>
+      <c r="C130" s="44"/>
+      <c r="D130" s="44"/>
+      <c r="E130" s="44"/>
+      <c r="F130" s="44"/>
+      <c r="G130" s="44"/>
+      <c r="H130" s="44"/>
+      <c r="I130" s="44"/>
+      <c r="J130" s="44"/>
     </row>
     <row r="131" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B131" s="37"/>
-      <c r="C131" s="37"/>
-      <c r="D131" s="37"/>
-      <c r="E131" s="37"/>
-      <c r="F131" s="37"/>
-      <c r="G131" s="37"/>
-      <c r="H131" s="37"/>
-      <c r="I131" s="37"/>
-      <c r="J131" s="37"/>
+      <c r="B131" s="44"/>
+      <c r="C131" s="44"/>
+      <c r="D131" s="44"/>
+      <c r="E131" s="44"/>
+      <c r="F131" s="44"/>
+      <c r="G131" s="44"/>
+      <c r="H131" s="44"/>
+      <c r="I131" s="44"/>
+      <c r="J131" s="44"/>
     </row>
     <row r="132" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="133" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B133" s="36" t="s">
+      <c r="B133" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="C133" s="37"/>
-      <c r="D133" s="37"/>
-      <c r="E133" s="37"/>
-      <c r="F133" s="37"/>
-      <c r="G133" s="37"/>
-      <c r="H133" s="37"/>
-      <c r="I133" s="37"/>
-      <c r="J133" s="37"/>
+      <c r="C133" s="44"/>
+      <c r="D133" s="44"/>
+      <c r="E133" s="44"/>
+      <c r="F133" s="44"/>
+      <c r="G133" s="44"/>
+      <c r="H133" s="44"/>
+      <c r="I133" s="44"/>
+      <c r="J133" s="44"/>
     </row>
     <row r="134" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B134" s="37"/>
-      <c r="C134" s="37"/>
-      <c r="D134" s="37"/>
-      <c r="E134" s="37"/>
-      <c r="F134" s="37"/>
-      <c r="G134" s="37"/>
-      <c r="H134" s="37"/>
-      <c r="I134" s="37"/>
-      <c r="J134" s="37"/>
+      <c r="B134" s="44"/>
+      <c r="C134" s="44"/>
+      <c r="D134" s="44"/>
+      <c r="E134" s="44"/>
+      <c r="F134" s="44"/>
+      <c r="G134" s="44"/>
+      <c r="H134" s="44"/>
+      <c r="I134" s="44"/>
+      <c r="J134" s="44"/>
     </row>
     <row r="135" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B135" s="37"/>
-      <c r="C135" s="37"/>
-      <c r="D135" s="37"/>
-      <c r="E135" s="37"/>
-      <c r="F135" s="37"/>
-      <c r="G135" s="37"/>
-      <c r="H135" s="37"/>
-      <c r="I135" s="37"/>
-      <c r="J135" s="37"/>
+      <c r="B135" s="44"/>
+      <c r="C135" s="44"/>
+      <c r="D135" s="44"/>
+      <c r="E135" s="44"/>
+      <c r="F135" s="44"/>
+      <c r="G135" s="44"/>
+      <c r="H135" s="44"/>
+      <c r="I135" s="44"/>
+      <c r="J135" s="44"/>
     </row>
     <row r="136" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B136" s="37"/>
-      <c r="C136" s="37"/>
-      <c r="D136" s="37"/>
-      <c r="E136" s="37"/>
-      <c r="F136" s="37"/>
-      <c r="G136" s="37"/>
-      <c r="H136" s="37"/>
-      <c r="I136" s="37"/>
-      <c r="J136" s="37"/>
+      <c r="B136" s="44"/>
+      <c r="C136" s="44"/>
+      <c r="D136" s="44"/>
+      <c r="E136" s="44"/>
+      <c r="F136" s="44"/>
+      <c r="G136" s="44"/>
+      <c r="H136" s="44"/>
+      <c r="I136" s="44"/>
+      <c r="J136" s="44"/>
     </row>
     <row r="137" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B137" s="37"/>
-      <c r="C137" s="37"/>
-      <c r="D137" s="37"/>
-      <c r="E137" s="37"/>
-      <c r="F137" s="37"/>
-      <c r="G137" s="37"/>
-      <c r="H137" s="37"/>
-      <c r="I137" s="37"/>
-      <c r="J137" s="37"/>
+      <c r="B137" s="44"/>
+      <c r="C137" s="44"/>
+      <c r="D137" s="44"/>
+      <c r="E137" s="44"/>
+      <c r="F137" s="44"/>
+      <c r="G137" s="44"/>
+      <c r="H137" s="44"/>
+      <c r="I137" s="44"/>
+      <c r="J137" s="44"/>
     </row>
     <row r="138" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B138" s="37"/>
-      <c r="C138" s="37"/>
-      <c r="D138" s="37"/>
-      <c r="E138" s="37"/>
-      <c r="F138" s="37"/>
-      <c r="G138" s="37"/>
-      <c r="H138" s="37"/>
-      <c r="I138" s="37"/>
-      <c r="J138" s="37"/>
+      <c r="B138" s="44"/>
+      <c r="C138" s="44"/>
+      <c r="D138" s="44"/>
+      <c r="E138" s="44"/>
+      <c r="F138" s="44"/>
+      <c r="G138" s="44"/>
+      <c r="H138" s="44"/>
+      <c r="I138" s="44"/>
+      <c r="J138" s="44"/>
     </row>
     <row r="139" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B139" s="37"/>
-      <c r="C139" s="37"/>
-      <c r="D139" s="37"/>
-      <c r="E139" s="37"/>
-      <c r="F139" s="37"/>
-      <c r="G139" s="37"/>
-      <c r="H139" s="37"/>
-      <c r="I139" s="37"/>
-      <c r="J139" s="37"/>
+      <c r="B139" s="44"/>
+      <c r="C139" s="44"/>
+      <c r="D139" s="44"/>
+      <c r="E139" s="44"/>
+      <c r="F139" s="44"/>
+      <c r="G139" s="44"/>
+      <c r="H139" s="44"/>
+      <c r="I139" s="44"/>
+      <c r="J139" s="44"/>
     </row>
     <row r="140" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B140" s="37"/>
-      <c r="C140" s="37"/>
-      <c r="D140" s="37"/>
-      <c r="E140" s="37"/>
-      <c r="F140" s="37"/>
-      <c r="G140" s="37"/>
-      <c r="H140" s="37"/>
-      <c r="I140" s="37"/>
-      <c r="J140" s="37"/>
+      <c r="B140" s="44"/>
+      <c r="C140" s="44"/>
+      <c r="D140" s="44"/>
+      <c r="E140" s="44"/>
+      <c r="F140" s="44"/>
+      <c r="G140" s="44"/>
+      <c r="H140" s="44"/>
+      <c r="I140" s="44"/>
+      <c r="J140" s="44"/>
     </row>
     <row r="141" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B141" s="37"/>
-      <c r="C141" s="37"/>
-      <c r="D141" s="37"/>
-      <c r="E141" s="37"/>
-      <c r="F141" s="37"/>
-      <c r="G141" s="37"/>
-      <c r="H141" s="37"/>
-      <c r="I141" s="37"/>
-      <c r="J141" s="37"/>
+      <c r="B141" s="44"/>
+      <c r="C141" s="44"/>
+      <c r="D141" s="44"/>
+      <c r="E141" s="44"/>
+      <c r="F141" s="44"/>
+      <c r="G141" s="44"/>
+      <c r="H141" s="44"/>
+      <c r="I141" s="44"/>
+      <c r="J141" s="44"/>
     </row>
     <row r="142" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="143" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B143" s="38" t="s">
+      <c r="B143" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="C143" s="37"/>
-      <c r="D143" s="37"/>
-      <c r="E143" s="37"/>
-      <c r="F143" s="37"/>
-      <c r="G143" s="37"/>
-      <c r="H143" s="37"/>
-      <c r="I143" s="37"/>
-      <c r="J143" s="37"/>
+      <c r="C143" s="44"/>
+      <c r="D143" s="44"/>
+      <c r="E143" s="44"/>
+      <c r="F143" s="44"/>
+      <c r="G143" s="44"/>
+      <c r="H143" s="44"/>
+      <c r="I143" s="44"/>
+      <c r="J143" s="44"/>
     </row>
     <row r="144" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B144" s="37"/>
-      <c r="C144" s="37"/>
-      <c r="D144" s="37"/>
-      <c r="E144" s="37"/>
-      <c r="F144" s="37"/>
-      <c r="G144" s="37"/>
-      <c r="H144" s="37"/>
-      <c r="I144" s="37"/>
-      <c r="J144" s="37"/>
+      <c r="B144" s="44"/>
+      <c r="C144" s="44"/>
+      <c r="D144" s="44"/>
+      <c r="E144" s="44"/>
+      <c r="F144" s="44"/>
+      <c r="G144" s="44"/>
+      <c r="H144" s="44"/>
+      <c r="I144" s="44"/>
+      <c r="J144" s="44"/>
     </row>
     <row r="145" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B145" s="37"/>
-      <c r="C145" s="37"/>
-      <c r="D145" s="37"/>
-      <c r="E145" s="37"/>
-      <c r="F145" s="37"/>
-      <c r="G145" s="37"/>
-      <c r="H145" s="37"/>
-      <c r="I145" s="37"/>
-      <c r="J145" s="37"/>
+      <c r="B145" s="44"/>
+      <c r="C145" s="44"/>
+      <c r="D145" s="44"/>
+      <c r="E145" s="44"/>
+      <c r="F145" s="44"/>
+      <c r="G145" s="44"/>
+      <c r="H145" s="44"/>
+      <c r="I145" s="44"/>
+      <c r="J145" s="44"/>
     </row>
     <row r="146" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B146" s="37"/>
-      <c r="C146" s="37"/>
-      <c r="D146" s="37"/>
-      <c r="E146" s="37"/>
-      <c r="F146" s="37"/>
-      <c r="G146" s="37"/>
-      <c r="H146" s="37"/>
-      <c r="I146" s="37"/>
-      <c r="J146" s="37"/>
+      <c r="B146" s="44"/>
+      <c r="C146" s="44"/>
+      <c r="D146" s="44"/>
+      <c r="E146" s="44"/>
+      <c r="F146" s="44"/>
+      <c r="G146" s="44"/>
+      <c r="H146" s="44"/>
+      <c r="I146" s="44"/>
+      <c r="J146" s="44"/>
     </row>
     <row r="147" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B147" s="37"/>
-      <c r="C147" s="37"/>
-      <c r="D147" s="37"/>
-      <c r="E147" s="37"/>
-      <c r="F147" s="37"/>
-      <c r="G147" s="37"/>
-      <c r="H147" s="37"/>
-      <c r="I147" s="37"/>
-      <c r="J147" s="37"/>
+      <c r="B147" s="44"/>
+      <c r="C147" s="44"/>
+      <c r="D147" s="44"/>
+      <c r="E147" s="44"/>
+      <c r="F147" s="44"/>
+      <c r="G147" s="44"/>
+      <c r="H147" s="44"/>
+      <c r="I147" s="44"/>
+      <c r="J147" s="44"/>
     </row>
     <row r="148" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D148" s="17" t="s">
@@ -23207,7 +23192,7 @@
       </c>
       <c r="F480" s="27"/>
       <c r="G480" s="27" t="s">
-        <v>1930</v>
+        <v>1939</v>
       </c>
       <c r="H480" s="27" t="s">
         <v>1624</v>
@@ -23232,7 +23217,7 @@
       </c>
       <c r="F481" s="27"/>
       <c r="G481" s="27" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="H481" s="27" t="s">
         <v>1624</v>
@@ -23243,7 +23228,7 @@
       <c r="A482" s="35" t="s">
         <v>1851</v>
       </c>
-      <c r="B482" s="39" t="s">
+      <c r="B482" s="36" t="s">
         <v>1852</v>
       </c>
       <c r="C482" s="24" t="s">
@@ -23263,437 +23248,437 @@
       <c r="I482" s="24"/>
     </row>
     <row r="483" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A483" s="40" t="s">
+      <c r="A483" s="37" t="s">
         <v>1855</v>
       </c>
-      <c r="B483" s="41" t="s">
+      <c r="B483" s="38" t="s">
         <v>1856</v>
       </c>
-      <c r="C483" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="D483" s="43" t="s">
+      <c r="C483" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D483" s="40" t="s">
         <v>1857</v>
       </c>
-      <c r="E483" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="F483" s="43" t="s">
+      <c r="E483" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F483" s="40" t="s">
         <v>1858</v>
       </c>
-      <c r="G483" s="43" t="s">
+      <c r="G483" s="40" t="s">
         <v>1921</v>
       </c>
-      <c r="H483" s="43" t="s">
+      <c r="H483" s="40" t="s">
         <v>1854</v>
       </c>
-      <c r="I483" s="44" t="s">
+      <c r="I483" s="41" t="s">
         <v>1859</v>
       </c>
     </row>
     <row r="484" spans="1:9" ht="78" x14ac:dyDescent="0.3">
-      <c r="A484" s="45" t="s">
+      <c r="A484" s="37" t="s">
         <v>1860</v>
       </c>
-      <c r="B484" s="46" t="s">
+      <c r="B484" s="38" t="s">
         <v>1861</v>
       </c>
-      <c r="C484" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="D484" s="48" t="s">
+      <c r="C484" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D484" s="40" t="s">
         <v>1862</v>
       </c>
-      <c r="E484" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F484" s="48"/>
-      <c r="G484" s="48"/>
-      <c r="H484" s="48" t="s">
+      <c r="E484" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F484" s="40"/>
+      <c r="G484" s="40"/>
+      <c r="H484" s="40" t="s">
         <v>1854</v>
       </c>
-      <c r="I484" s="49" t="s">
+      <c r="I484" s="41" t="s">
         <v>1863</v>
       </c>
     </row>
     <row r="485" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A485" s="45" t="s">
+      <c r="A485" s="37" t="s">
         <v>1864</v>
       </c>
-      <c r="B485" s="46" t="s">
+      <c r="B485" s="38" t="s">
         <v>1923</v>
       </c>
-      <c r="C485" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="D485" s="48" t="s">
+      <c r="C485" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D485" s="40" t="s">
         <v>1865</v>
       </c>
-      <c r="E485" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F485" s="48" t="s">
+      <c r="E485" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F485" s="40" t="s">
         <v>1924</v>
       </c>
-      <c r="G485" s="48"/>
-      <c r="H485" s="48" t="s">
+      <c r="G485" s="40"/>
+      <c r="H485" s="40" t="s">
         <v>1854</v>
       </c>
-      <c r="I485" s="49" t="s">
+      <c r="I485" s="41" t="s">
         <v>1866</v>
       </c>
     </row>
     <row r="486" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A486" s="45" t="s">
+      <c r="A486" s="37" t="s">
         <v>1867</v>
       </c>
-      <c r="B486" s="46" t="s">
+      <c r="B486" s="38" t="s">
         <v>1868</v>
       </c>
-      <c r="C486" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="D486" s="48" t="s">
+      <c r="C486" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D486" s="40" t="s">
         <v>1869</v>
       </c>
-      <c r="E486" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F486" s="48" t="s">
+      <c r="E486" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F486" s="40" t="s">
         <v>1870</v>
       </c>
-      <c r="G486" s="48"/>
-      <c r="H486" s="48" t="s">
+      <c r="G486" s="40"/>
+      <c r="H486" s="40" t="s">
         <v>1854</v>
       </c>
-      <c r="I486" s="49" t="s">
+      <c r="I486" s="41" t="s">
         <v>1871</v>
       </c>
     </row>
     <row r="487" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A487" s="45" t="s">
+      <c r="A487" s="37" t="s">
         <v>1872</v>
       </c>
-      <c r="B487" s="46" t="s">
+      <c r="B487" s="38" t="s">
         <v>1926</v>
       </c>
-      <c r="C487" s="47" t="s">
+      <c r="C487" s="39" t="s">
         <v>84</v>
       </c>
       <c r="D487" s="25" t="s">
         <v>1927</v>
       </c>
-      <c r="E487" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F487" s="48"/>
-      <c r="G487" s="48"/>
-      <c r="H487" s="48" t="s">
+      <c r="E487" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F487" s="40"/>
+      <c r="G487" s="40"/>
+      <c r="H487" s="40" t="s">
         <v>1854</v>
       </c>
-      <c r="I487" s="49" t="s">
+      <c r="I487" s="41" t="s">
         <v>1873</v>
       </c>
     </row>
     <row r="488" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A488" s="45" t="s">
+      <c r="A488" s="37" t="s">
         <v>1874</v>
       </c>
-      <c r="B488" s="46" t="s">
+      <c r="B488" s="38" t="s">
         <v>1875</v>
       </c>
-      <c r="C488" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="D488" s="48" t="s">
+      <c r="C488" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D488" s="40" t="s">
         <v>1876</v>
       </c>
-      <c r="E488" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F488" s="48"/>
-      <c r="G488" s="48"/>
-      <c r="H488" s="48" t="s">
+      <c r="E488" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F488" s="40"/>
+      <c r="G488" s="40"/>
+      <c r="H488" s="40" t="s">
         <v>1854</v>
       </c>
-      <c r="I488" s="49" t="s">
+      <c r="I488" s="41" t="s">
         <v>1877</v>
       </c>
     </row>
     <row r="489" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A489" s="45" t="s">
+      <c r="A489" s="37" t="s">
         <v>1878</v>
       </c>
-      <c r="B489" s="46" t="s">
+      <c r="B489" s="38" t="s">
         <v>1879</v>
       </c>
-      <c r="C489" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="D489" s="48" t="s">
+      <c r="C489" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D489" s="40" t="s">
         <v>1880</v>
       </c>
-      <c r="E489" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F489" s="48" t="s">
+      <c r="E489" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F489" s="40" t="s">
         <v>1881</v>
       </c>
-      <c r="G489" s="48"/>
-      <c r="H489" s="48" t="s">
+      <c r="G489" s="40"/>
+      <c r="H489" s="40" t="s">
         <v>1854</v>
       </c>
-      <c r="I489" s="49" t="s">
+      <c r="I489" s="41" t="s">
         <v>1882</v>
       </c>
     </row>
     <row r="490" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A490" s="45" t="s">
+      <c r="A490" s="37" t="s">
         <v>1883</v>
       </c>
-      <c r="B490" s="46" t="s">
+      <c r="B490" s="38" t="s">
         <v>1884</v>
       </c>
-      <c r="C490" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="D490" s="48" t="s">
+      <c r="C490" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D490" s="40" t="s">
         <v>1885</v>
       </c>
-      <c r="E490" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F490" s="48" t="s">
+      <c r="E490" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F490" s="40" t="s">
         <v>1886</v>
       </c>
-      <c r="G490" s="48"/>
-      <c r="H490" s="48" t="s">
+      <c r="G490" s="40"/>
+      <c r="H490" s="40" t="s">
         <v>1854</v>
       </c>
-      <c r="I490" s="49" t="s">
+      <c r="I490" s="41" t="s">
         <v>1887</v>
       </c>
     </row>
     <row r="491" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A491" s="45" t="s">
+      <c r="A491" s="37" t="s">
         <v>1888</v>
       </c>
-      <c r="B491" s="46" t="s">
+      <c r="B491" s="38" t="s">
         <v>1889</v>
       </c>
-      <c r="C491" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="D491" s="48" t="s">
+      <c r="C491" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D491" s="40" t="s">
         <v>1890</v>
       </c>
-      <c r="E491" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F491" s="48" t="s">
+      <c r="E491" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F491" s="40" t="s">
         <v>1891</v>
       </c>
-      <c r="G491" s="48"/>
-      <c r="H491" s="48" t="s">
+      <c r="G491" s="40"/>
+      <c r="H491" s="40" t="s">
         <v>1854</v>
       </c>
-      <c r="I491" s="49" t="s">
+      <c r="I491" s="41" t="s">
         <v>1892</v>
       </c>
     </row>
     <row r="492" spans="1:9" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="A492" s="45" t="s">
+      <c r="A492" s="37" t="s">
         <v>1893</v>
       </c>
-      <c r="B492" s="46" t="s">
+      <c r="B492" s="38" t="s">
         <v>1894</v>
       </c>
-      <c r="C492" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="D492" s="48" t="s">
+      <c r="C492" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D492" s="40" t="s">
         <v>1895</v>
       </c>
-      <c r="E492" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F492" s="48"/>
-      <c r="G492" s="48"/>
-      <c r="H492" s="48" t="s">
+      <c r="E492" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F492" s="40"/>
+      <c r="G492" s="40"/>
+      <c r="H492" s="40" t="s">
         <v>1854</v>
       </c>
-      <c r="I492" s="49" t="s">
+      <c r="I492" s="41" t="s">
         <v>1896</v>
       </c>
     </row>
     <row r="493" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A493" s="45" t="s">
+      <c r="A493" s="37" t="s">
         <v>1897</v>
       </c>
-      <c r="B493" s="46" t="s">
+      <c r="B493" s="38" t="s">
         <v>1898</v>
       </c>
-      <c r="C493" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="D493" s="48" t="s">
+      <c r="C493" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D493" s="40" t="s">
         <v>1899</v>
       </c>
-      <c r="E493" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F493" s="48"/>
-      <c r="G493" s="48"/>
-      <c r="H493" s="48" t="s">
+      <c r="E493" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F493" s="40"/>
+      <c r="G493" s="40"/>
+      <c r="H493" s="40" t="s">
         <v>1854</v>
       </c>
-      <c r="I493" s="49" t="s">
+      <c r="I493" s="41" t="s">
         <v>1900</v>
       </c>
     </row>
     <row r="494" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A494" s="45" t="s">
+      <c r="A494" s="37" t="s">
         <v>1901</v>
       </c>
-      <c r="B494" s="46" t="s">
+      <c r="B494" s="38" t="s">
         <v>1902</v>
       </c>
-      <c r="C494" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="D494" s="48" t="s">
+      <c r="C494" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D494" s="40" t="s">
         <v>1903</v>
       </c>
-      <c r="E494" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F494" s="48"/>
-      <c r="G494" s="48"/>
-      <c r="H494" s="48" t="s">
+      <c r="E494" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F494" s="40"/>
+      <c r="G494" s="40"/>
+      <c r="H494" s="40" t="s">
         <v>1854</v>
       </c>
-      <c r="I494" s="49" t="s">
+      <c r="I494" s="41" t="s">
         <v>1904</v>
       </c>
     </row>
     <row r="495" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A495" s="45" t="s">
+      <c r="A495" s="37" t="s">
         <v>1905</v>
       </c>
-      <c r="B495" s="46" t="s">
+      <c r="B495" s="38" t="s">
         <v>1906</v>
       </c>
-      <c r="C495" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="D495" s="48" t="s">
+      <c r="C495" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D495" s="40" t="s">
         <v>1907</v>
       </c>
-      <c r="E495" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F495" s="48"/>
-      <c r="G495" s="48"/>
-      <c r="H495" s="48" t="s">
+      <c r="E495" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F495" s="40"/>
+      <c r="G495" s="40"/>
+      <c r="H495" s="40" t="s">
         <v>1854</v>
       </c>
-      <c r="I495" s="49" t="s">
+      <c r="I495" s="41" t="s">
         <v>1908</v>
       </c>
     </row>
     <row r="496" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A496" s="45" t="s">
+      <c r="A496" s="37" t="s">
         <v>1909</v>
       </c>
-      <c r="B496" s="46" t="s">
+      <c r="B496" s="38" t="s">
         <v>1910</v>
       </c>
-      <c r="C496" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="D496" s="48" t="s">
+      <c r="C496" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D496" s="40" t="s">
         <v>1911</v>
       </c>
-      <c r="E496" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F496" s="48"/>
-      <c r="G496" s="48"/>
-      <c r="H496" s="48" t="s">
+      <c r="E496" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F496" s="40"/>
+      <c r="G496" s="40"/>
+      <c r="H496" s="40" t="s">
         <v>1854</v>
       </c>
-      <c r="I496" s="49" t="s">
+      <c r="I496" s="41" t="s">
         <v>1912</v>
       </c>
     </row>
     <row r="497" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A497" s="45" t="s">
+      <c r="A497" s="37" t="s">
         <v>1913</v>
       </c>
-      <c r="B497" s="46" t="s">
+      <c r="B497" s="38" t="s">
         <v>1914</v>
       </c>
-      <c r="C497" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="D497" s="48" t="s">
+      <c r="C497" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D497" s="40" t="s">
         <v>1915</v>
       </c>
-      <c r="E497" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F497" s="48"/>
-      <c r="G497" s="48"/>
-      <c r="H497" s="48" t="s">
+      <c r="E497" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F497" s="40"/>
+      <c r="G497" s="40"/>
+      <c r="H497" s="40" t="s">
         <v>1854</v>
       </c>
-      <c r="I497" s="49" t="s">
+      <c r="I497" s="41" t="s">
         <v>1916</v>
       </c>
     </row>
     <row r="498" spans="1:9" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A498" s="45" t="s">
+      <c r="A498" s="37" t="s">
         <v>1917</v>
       </c>
-      <c r="B498" s="46" t="s">
+      <c r="B498" s="38" t="s">
         <v>1918</v>
       </c>
-      <c r="C498" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="D498" s="48" t="s">
+      <c r="C498" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D498" s="40" t="s">
         <v>1919</v>
       </c>
-      <c r="E498" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="F498" s="48"/>
-      <c r="G498" s="48"/>
-      <c r="H498" s="48" t="s">
+      <c r="E498" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F498" s="40"/>
+      <c r="G498" s="40"/>
+      <c r="H498" s="40" t="s">
         <v>1854</v>
       </c>
-      <c r="I498" s="49" t="s">
+      <c r="I498" s="41" t="s">
         <v>1920</v>
       </c>
     </row>
     <row r="499" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A499" s="35" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B499" s="36" t="s">
         <v>1931</v>
       </c>
-      <c r="B499" s="39" t="s">
+      <c r="C499" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D499" s="42" t="s">
         <v>1932</v>
       </c>
-      <c r="C499" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D499" s="50" t="s">
+      <c r="E499" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="F499" s="24" t="s">
         <v>1933</v>
-      </c>
-      <c r="E499" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="F499" s="24" t="s">
-        <v>1934</v>
       </c>
       <c r="G499" s="24"/>
       <c r="H499" s="25" t="s">
@@ -23703,22 +23688,22 @@
     </row>
     <row r="500" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A500" s="35" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B500" s="36" t="s">
         <v>1935</v>
       </c>
-      <c r="B500" s="39" t="s">
+      <c r="C500" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D500" s="25" t="s">
         <v>1936</v>
       </c>
-      <c r="C500" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D500" s="25" t="s">
+      <c r="E500" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="F500" s="24" t="s">
         <v>1937</v>
-      </c>
-      <c r="E500" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="F500" s="24" t="s">
-        <v>1938</v>
       </c>
       <c r="G500" s="24"/>
       <c r="H500" s="25" t="s">

--- a/inbox-excel-vocabs/voc4cat.xlsx
+++ b/inbox-excel-vocabs/voc4cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\working group\Franzi\Research Data Managment\Voc4Cat\FF_20250328_Voc4Cat contributions\Revision ab august\selected concepts 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{347A717F-27FD-45B2-B2A2-28317099230E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF15B856-0238-422E-A795-6F4F65CF9611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="652" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6606,35 +6606,10 @@
     <t>voc4cat:0007795 (co-precipitation)</t>
   </si>
   <si>
-    <t>voc4cat:00007806 (incipient wetness impregnation)</t>
-  </si>
-  <si>
     <t>operando analysis</t>
   </si>
   <si>
     <t>operando characterization</t>
-  </si>
-  <si>
-    <t>voc4cat:0000067 (X-ray fluorescence),
-voc4cat:0000068 (electron energy loss spectroscopy),
-voc4cat:0000069 (Raman spectroscopy),
-voc4cat:0000070 (atomic force microscopy),
-voc4cat:0000071 (differential scanning calorimetry),
-voc4cat:0000072 (thermogravimetric analysis),
-voc4cat:0000073 (nuclear magnetic resonance spectroscopy),
-voc4cat:0000074 (photoluminescence),
-voc4cat:0000075 (scanning electron microscopy),
-voc4cat:0000076 (X-ray photoelectron spectroscopy),
-voc4cat:0000077 (X-ray diffraction),
-voc4cat:0000078 (transmission electron microscopy),
-voc4cat:0000079 (ultraviolet-visible spectroscopy),
-voc4cat:0000080 (Fourier transform infrared spectroscopy),
-voc4cat:0000081 (Brunauer-Emmett-Teller surface area analysis),
-voc4cat:0000083 (Mott-Schottky analysis),
-voc4cat:0000286 (X-ray absorption spectroscopy),
-voc4cat:0000288 (electron microscopy),
-voc4cat:0007807 (in-operando analysis),
-voc4cat:0007808 (in-situ analysis)</t>
   </si>
   <si>
     <t>atmosphere</t>
@@ -6845,6 +6820,31 @@
 voc4cat:0007809 (atmosphere),
 voc4cat:0007838 (product mixture),
 voc4cat:0007793 (additive)</t>
+  </si>
+  <si>
+    <t>voc4cat:0000067 (X-ray fluorescence),
+voc4cat:0000068 (electron energy loss spectroscopy),
+voc4cat:0000069 (Raman spectroscopy),
+voc4cat:0000070 (atomic force microscopy),
+voc4cat:0000071 (differential scanning calorimetry),
+voc4cat:0000072 (thermogravimetric analysis),
+voc4cat:0000073 (nuclear magnetic resonance spectroscopy),
+voc4cat:0000074 (photoluminescence),
+voc4cat:0000075 (scanning electron microscopy),
+voc4cat:0000076 (X-ray photoelectron spectroscopy),
+voc4cat:0000077 (X-ray diffraction),
+voc4cat:0000078 (transmission electron microscopy),
+voc4cat:0000079 (ultraviolet-visible spectroscopy),
+voc4cat:0000080 (Fourier transform infrared spectroscopy),
+voc4cat:0000081 (Brunauer-Emmett-Teller surface area analysis),
+voc4cat:0000083 (Mott-Schottky analysis),
+voc4cat:0000286 (X-ray absorption spectroscopy),
+voc4cat:0000288 (electron microscopy),
+voc4cat:0007807 (operando analysis),
+voc4cat:0007808 (in-situ analysis)</t>
+  </si>
+  <si>
+    <t>voc4cat:0007806 (incipient wetness impregnation)</t>
   </si>
 </sst>
 </file>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="27" t="s">
-        <v>1922</v>
+        <v>1939</v>
       </c>
       <c r="H78" s="27" t="s">
         <v>252</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="F237" s="27"/>
       <c r="G237" s="27" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="H237" s="27" t="s">
         <v>93</v>
@@ -21190,7 +21190,7 @@
         <v>1410</v>
       </c>
       <c r="G400" s="27" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="H400" s="27" t="s">
         <v>93</v>
@@ -23067,7 +23067,7 @@
         <v>1709</v>
       </c>
       <c r="G475" s="27" t="s">
-        <v>1925</v>
+        <v>1938</v>
       </c>
       <c r="H475" s="27" t="s">
         <v>93</v>
@@ -23192,7 +23192,7 @@
       </c>
       <c r="F480" s="27"/>
       <c r="G480" s="27" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="H480" s="27" t="s">
         <v>1624</v>
@@ -23217,7 +23217,7 @@
       </c>
       <c r="F481" s="27"/>
       <c r="G481" s="27" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="H481" s="27" t="s">
         <v>1624</v>
@@ -23306,7 +23306,7 @@
         <v>1864</v>
       </c>
       <c r="B485" s="38" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="C485" s="39" t="s">
         <v>84</v>
@@ -23318,7 +23318,7 @@
         <v>84</v>
       </c>
       <c r="F485" s="40" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="G485" s="40"/>
       <c r="H485" s="40" t="s">
@@ -23360,13 +23360,13 @@
         <v>1872</v>
       </c>
       <c r="B487" s="38" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="C487" s="39" t="s">
         <v>84</v>
       </c>
       <c r="D487" s="25" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="E487" s="39" t="s">
         <v>84</v>
@@ -23663,22 +23663,22 @@
     </row>
     <row r="499" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A499" s="35" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B499" s="36" t="s">
+        <v>1929</v>
+      </c>
+      <c r="C499" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D499" s="42" t="s">
         <v>1930</v>
       </c>
-      <c r="B499" s="36" t="s">
+      <c r="E499" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="F499" s="24" t="s">
         <v>1931</v>
-      </c>
-      <c r="C499" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D499" s="42" t="s">
-        <v>1932</v>
-      </c>
-      <c r="E499" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="F499" s="24" t="s">
-        <v>1933</v>
       </c>
       <c r="G499" s="24"/>
       <c r="H499" s="25" t="s">
@@ -23688,22 +23688,22 @@
     </row>
     <row r="500" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A500" s="35" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B500" s="36" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C500" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D500" s="25" t="s">
         <v>1934</v>
       </c>
-      <c r="B500" s="36" t="s">
+      <c r="E500" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="F500" s="24" t="s">
         <v>1935</v>
-      </c>
-      <c r="C500" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="D500" s="25" t="s">
-        <v>1936</v>
-      </c>
-      <c r="E500" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="F500" s="24" t="s">
-        <v>1937</v>
       </c>
       <c r="G500" s="24"/>
       <c r="H500" s="25" t="s">
